--- a/past_data/site_8023/2026-09-01.xlsx
+++ b/past_data/site_8023/2026-09-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="67">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>343.6</t>
+    <t>422.5</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.4</t>
+    <t>4.2</t>
   </si>
   <si>
     <t>01일</t>
@@ -101,16 +101,52 @@
     <t>05일</t>
   </si>
   <si>
+    <t>523.0</t>
+  </si>
+  <si>
+    <t>1897.3</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>19.0</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
+    <t>495.0</t>
+  </si>
+  <si>
+    <t>2392.3</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>23.9</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
+    <t>565.0</t>
+  </si>
+  <si>
+    <t>2957.3</t>
+  </si>
+  <si>
+    <t>5.7</t>
+  </si>
+  <si>
+    <t>29.6</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>06일</t>
-  </si>
-  <si>
-    <t>07일</t>
-  </si>
-  <si>
-    <t>08일</t>
   </si>
   <si>
     <t>09일</t>
@@ -570,13 +606,13 @@
         <v>29</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -584,19 +620,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -604,19 +640,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>29</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -624,19 +660,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -644,19 +680,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -664,19 +700,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -684,19 +720,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -704,19 +740,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -724,19 +760,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -744,19 +780,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -764,19 +800,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -784,19 +820,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -804,19 +840,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -824,19 +860,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -844,19 +880,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -864,19 +900,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -884,19 +920,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -904,19 +940,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -924,19 +960,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -944,19 +980,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -964,19 +1000,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -984,19 +1020,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1004,19 +1040,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1024,19 +1060,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1044,19 +1080,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1064,19 +1100,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-09-01.xlsx
+++ b/past_data/site_8023/2026-09-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="71">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>422.5</t>
+    <t>437.7</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.2</t>
+    <t>4.4</t>
   </si>
   <si>
     <t>01일</t>
@@ -146,10 +146,22 @@
     <t>08일</t>
   </si>
   <si>
+    <t>544.2</t>
+  </si>
+  <si>
+    <t>3501.5</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
+    <t>35.0</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>09일</t>
   </si>
   <si>
     <t>10일</t>
@@ -666,13 +678,13 @@
         <v>44</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -680,19 +692,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -700,19 +712,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -720,19 +732,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -740,19 +752,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -760,19 +772,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -780,19 +792,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -800,19 +812,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -820,19 +832,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -840,19 +852,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -860,19 +872,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -880,19 +892,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -900,19 +912,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -920,19 +932,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -940,19 +952,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -960,19 +972,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -980,19 +992,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1000,19 +1012,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1020,19 +1032,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1040,19 +1052,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1060,19 +1072,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1080,19 +1092,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1100,19 +1112,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-09-01.xlsx
+++ b/past_data/site_8023/2026-09-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="75">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>437.7</t>
+    <t>439.1</t>
   </si>
   <si>
     <t>-</t>
@@ -161,10 +161,22 @@
     <t>09일</t>
   </si>
   <si>
+    <t>450.5</t>
+  </si>
+  <si>
+    <t>3952.0</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>39.5</t>
+  </si>
+  <si>
+    <t>10일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>10일</t>
   </si>
   <si>
     <t>11일</t>
@@ -698,13 +710,13 @@
         <v>49</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -712,19 +724,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -732,19 +744,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -752,19 +764,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -772,19 +784,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -792,19 +804,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -812,19 +824,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -832,19 +844,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -852,19 +864,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -872,19 +884,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -892,19 +904,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -912,19 +924,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -932,19 +944,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -952,19 +964,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -972,19 +984,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -992,19 +1004,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1012,19 +1024,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1032,19 +1044,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1052,19 +1064,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1072,19 +1084,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1092,19 +1104,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1112,19 +1124,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-09-01.xlsx
+++ b/past_data/site_8023/2026-09-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="79">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>439.1</t>
+    <t>412.0</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.4</t>
+    <t>4.1</t>
   </si>
   <si>
     <t>01일</t>
@@ -176,10 +176,22 @@
     <t>10일</t>
   </si>
   <si>
+    <t>168.1</t>
+  </si>
+  <si>
+    <t>4120.1</t>
+  </si>
+  <si>
+    <t>1.7</t>
+  </si>
+  <si>
+    <t>41.2</t>
+  </si>
+  <si>
+    <t>11일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>11일</t>
   </si>
   <si>
     <t>12일</t>
@@ -730,13 +742,13 @@
         <v>54</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -744,19 +756,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -764,19 +776,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -784,19 +796,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -804,19 +816,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -824,19 +836,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -844,19 +856,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -864,19 +876,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -884,19 +896,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -904,19 +916,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -924,19 +936,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -944,19 +956,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -964,19 +976,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -984,19 +996,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1004,19 +1016,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1024,19 +1036,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1044,19 +1056,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1064,19 +1076,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1084,19 +1096,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1104,19 +1116,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1124,19 +1136,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-09-01.xlsx
+++ b/past_data/site_8023/2026-09-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="93">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>412.0</t>
+    <t>380.5</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.1</t>
+    <t>3.8</t>
   </si>
   <si>
     <t>01일</t>
@@ -191,19 +191,61 @@
     <t>11일</t>
   </si>
   <si>
+    <t>531.9</t>
+  </si>
+  <si>
+    <t>4652.0</t>
+  </si>
+  <si>
+    <t>46.5</t>
+  </si>
+  <si>
+    <t>12일</t>
+  </si>
+  <si>
+    <t>202.8</t>
+  </si>
+  <si>
+    <t>4854.8</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t>48.5</t>
+  </si>
+  <si>
+    <t>13일</t>
+  </si>
+  <si>
+    <t>181.1</t>
+  </si>
+  <si>
+    <t>5035.9</t>
+  </si>
+  <si>
+    <t>1.8</t>
+  </si>
+  <si>
+    <t>50.4</t>
+  </si>
+  <si>
+    <t>14일</t>
+  </si>
+  <si>
+    <t>291.7</t>
+  </si>
+  <si>
+    <t>5327.6</t>
+  </si>
+  <si>
+    <t>53.3</t>
+  </si>
+  <si>
+    <t>15일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>12일</t>
-  </si>
-  <si>
-    <t>13일</t>
-  </si>
-  <si>
-    <t>14일</t>
-  </si>
-  <si>
-    <t>15일</t>
   </si>
   <si>
     <t>16일</t>
@@ -762,13 +804,13 @@
         <v>59</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -776,19 +818,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -796,19 +838,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>59</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -816,19 +858,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>59</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -836,19 +878,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -856,19 +898,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -876,19 +918,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -896,19 +938,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -916,19 +958,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -936,19 +978,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -956,19 +998,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -976,19 +1018,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -996,19 +1038,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1016,19 +1058,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1036,19 +1078,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1056,19 +1098,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1076,19 +1118,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1096,19 +1138,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1116,19 +1158,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1136,19 +1178,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-09-01.xlsx
+++ b/past_data/site_8023/2026-09-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="94">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>380.5</t>
+    <t>384.2</t>
   </si>
   <si>
     <t>-</t>
@@ -233,13 +233,16 @@
     <t>14일</t>
   </si>
   <si>
-    <t>291.7</t>
-  </si>
-  <si>
-    <t>5327.6</t>
-  </si>
-  <si>
-    <t>53.3</t>
+    <t>343.3</t>
+  </si>
+  <si>
+    <t>5379.2</t>
+  </si>
+  <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>53.8</t>
   </si>
   <si>
     <t>15일</t>
@@ -867,10 +870,10 @@
         <v>74</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -878,19 +881,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -898,19 +901,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -918,19 +921,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -938,19 +941,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -958,19 +961,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -978,19 +981,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -998,19 +1001,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1018,19 +1021,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1038,19 +1041,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1058,19 +1061,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1078,19 +1081,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1098,19 +1101,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1118,19 +1121,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1138,19 +1141,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1158,19 +1161,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1178,19 +1181,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-09-01.xlsx
+++ b/past_data/site_8023/2026-09-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="97">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>384.2</t>
+    <t>392.1</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.8</t>
+    <t>3.9</t>
   </si>
   <si>
     <t>01일</t>
@@ -248,10 +248,19 @@
     <t>15일</t>
   </si>
   <si>
+    <t>502.1</t>
+  </si>
+  <si>
+    <t>5881.3</t>
+  </si>
+  <si>
+    <t>58.8</t>
+  </si>
+  <si>
+    <t>16일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>16일</t>
   </si>
   <si>
     <t>17일</t>
@@ -887,13 +896,13 @@
         <v>78</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -901,19 +910,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -921,19 +930,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -941,19 +950,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -961,19 +970,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -981,19 +990,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1001,19 +1010,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1021,19 +1030,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1041,19 +1050,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1061,19 +1070,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1081,19 +1090,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1101,19 +1110,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1121,19 +1130,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1141,19 +1150,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1161,19 +1170,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1181,19 +1190,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-09-01.xlsx
+++ b/past_data/site_8023/2026-09-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="101">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>392.1</t>
+    <t>402.4</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.9</t>
+    <t>4.0</t>
   </si>
   <si>
     <t>01일</t>
@@ -260,10 +260,22 @@
     <t>16일</t>
   </si>
   <si>
+    <t>557.7</t>
+  </si>
+  <si>
+    <t>6439.0</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>64.4</t>
+  </si>
+  <si>
+    <t>17일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>17일</t>
   </si>
   <si>
     <t>18일</t>
@@ -916,13 +928,13 @@
         <v>82</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -930,19 +942,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -950,19 +962,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -970,19 +982,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -990,19 +1002,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1010,19 +1022,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1030,19 +1042,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1050,19 +1062,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1070,19 +1082,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1090,19 +1102,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1110,19 +1122,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1130,19 +1142,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1150,19 +1162,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1170,19 +1182,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1190,19 +1202,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-09-01.xlsx
+++ b/past_data/site_8023/2026-09-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="105">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>402.4</t>
+    <t>401.2</t>
   </si>
   <si>
     <t>-</t>
@@ -275,10 +275,22 @@
     <t>17일</t>
   </si>
   <si>
+    <t>381.4</t>
+  </si>
+  <si>
+    <t>6820.4</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>68.2</t>
+  </si>
+  <si>
+    <t>18일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>18일</t>
   </si>
   <si>
     <t>19일</t>
@@ -948,13 +960,13 @@
         <v>87</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -962,19 +974,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -982,19 +994,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1002,19 +1014,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1022,19 +1034,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1042,19 +1054,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1062,19 +1074,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1082,19 +1094,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1102,19 +1114,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1122,19 +1134,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1142,19 +1154,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1162,19 +1174,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1182,19 +1194,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1202,19 +1214,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-09-01.xlsx
+++ b/past_data/site_8023/2026-09-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="109">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>401.2</t>
+    <t>402.5</t>
   </si>
   <si>
     <t>-</t>
@@ -290,10 +290,22 @@
     <t>18일</t>
   </si>
   <si>
+    <t>424.9</t>
+  </si>
+  <si>
+    <t>7245.3</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>72.5</t>
+  </si>
+  <si>
+    <t>19일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>19일</t>
   </si>
   <si>
     <t>20일</t>
@@ -980,13 +992,13 @@
         <v>92</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -994,19 +1006,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1014,19 +1026,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1034,19 +1046,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1054,19 +1066,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1074,19 +1086,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1094,19 +1106,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1114,19 +1126,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1134,19 +1146,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1154,19 +1166,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1174,19 +1186,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1194,19 +1206,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1214,19 +1226,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-09-01.xlsx
+++ b/past_data/site_8023/2026-09-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="113">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>402.5</t>
+    <t>404.2</t>
   </si>
   <si>
     <t>-</t>
@@ -305,10 +305,22 @@
     <t>19일</t>
   </si>
   <si>
+    <t>433.8</t>
+  </si>
+  <si>
+    <t>7679.1</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>76.8</t>
+  </si>
+  <si>
+    <t>20일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>20일</t>
   </si>
   <si>
     <t>21일</t>
@@ -1012,13 +1024,13 @@
         <v>97</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1026,19 +1038,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1046,19 +1058,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1066,19 +1078,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1086,19 +1098,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1106,19 +1118,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1126,19 +1138,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1146,19 +1158,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1166,19 +1178,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1186,19 +1198,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1206,19 +1218,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1226,19 +1238,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-09-01.xlsx
+++ b/past_data/site_8023/2026-09-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="116">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>404.2</t>
+    <t>411.4</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.0</t>
+    <t>4.1</t>
   </si>
   <si>
     <t>01일</t>
@@ -320,10 +320,19 @@
     <t>20일</t>
   </si>
   <si>
+    <t>548.5</t>
+  </si>
+  <si>
+    <t>8227.6</t>
+  </si>
+  <si>
+    <t>82.3</t>
+  </si>
+  <si>
+    <t>21일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>21일</t>
   </si>
   <si>
     <t>22일</t>
@@ -1044,13 +1053,13 @@
         <v>102</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>102</v>
+        <v>26</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1058,19 +1067,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1078,19 +1087,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1098,19 +1107,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1118,19 +1127,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1138,19 +1147,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1158,19 +1167,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1178,19 +1187,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1198,19 +1207,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1218,19 +1227,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1238,19 +1247,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-09-01.xlsx
+++ b/past_data/site_8023/2026-09-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="121">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>411.4</t>
+    <t>420.4</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.1</t>
+    <t>4.2</t>
   </si>
   <si>
     <t>01일</t>
@@ -296,9 +296,6 @@
     <t>7245.3</t>
   </si>
   <si>
-    <t>4.2</t>
-  </si>
-  <si>
     <t>72.5</t>
   </si>
   <si>
@@ -332,13 +329,31 @@
     <t>21일</t>
   </si>
   <si>
+    <t>518.3</t>
+  </si>
+  <si>
+    <t>8745.9</t>
+  </si>
+  <si>
+    <t>87.5</t>
+  </si>
+  <si>
+    <t>22일</t>
+  </si>
+  <si>
+    <t>501.9</t>
+  </si>
+  <si>
+    <t>9247.8</t>
+  </si>
+  <si>
+    <t>92.5</t>
+  </si>
+  <si>
+    <t>23일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>22일</t>
-  </si>
-  <si>
-    <t>23일</t>
   </si>
   <si>
     <t>24일</t>
@@ -1016,10 +1031,10 @@
         <v>93</v>
       </c>
       <c r="E20" t="s" s="38">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s" s="39">
         <v>94</v>
-      </c>
-      <c r="F20" t="s" s="39">
-        <v>95</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1027,19 +1042,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
+        <v>95</v>
+      </c>
+      <c r="C21" t="s" s="31">
         <v>96</v>
       </c>
-      <c r="C21" t="s" s="31">
+      <c r="D21" t="s" s="32">
         <v>97</v>
       </c>
-      <c r="D21" t="s" s="32">
+      <c r="E21" t="s" s="33">
         <v>98</v>
       </c>
-      <c r="E21" t="s" s="33">
+      <c r="F21" t="s" s="34">
         <v>99</v>
-      </c>
-      <c r="F21" t="s" s="34">
-        <v>100</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1047,19 +1062,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
+        <v>100</v>
+      </c>
+      <c r="C22" t="s" s="36">
         <v>101</v>
       </c>
-      <c r="C22" t="s" s="36">
+      <c r="D22" t="s" s="37">
         <v>102</v>
-      </c>
-      <c r="D22" t="s" s="37">
-        <v>103</v>
       </c>
       <c r="E22" t="s" s="38">
         <v>26</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1067,19 +1082,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
+        <v>104</v>
+      </c>
+      <c r="C23" t="s" s="31">
         <v>105</v>
-      </c>
-      <c r="C23" t="s" s="31">
-        <v>106</v>
       </c>
       <c r="D23" t="s" s="32">
         <v>106</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1087,19 +1102,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1107,19 +1122,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1127,19 +1142,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1147,19 +1162,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1167,19 +1182,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1187,19 +1202,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1207,19 +1222,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1227,19 +1242,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1247,19 +1262,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-09-01.xlsx
+++ b/past_data/site_8023/2026-09-01.xlsx
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>420.4</t>
+    <t>420.5</t>
   </si>
   <si>
     <t>-</t>
@@ -341,10 +341,10 @@
     <t>22일</t>
   </si>
   <si>
-    <t>501.9</t>
-  </si>
-  <si>
-    <t>9247.8</t>
+    <t>504.3</t>
+  </si>
+  <si>
+    <t>9250.2</t>
   </si>
   <si>
     <t>92.5</t>

--- a/past_data/site_8023/2026-09-01.xlsx
+++ b/past_data/site_8023/2026-09-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="125">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>420.5</t>
+    <t>422.7</t>
   </si>
   <si>
     <t>-</t>
@@ -353,10 +353,22 @@
     <t>23일</t>
   </si>
   <si>
+    <t>471.9</t>
+  </si>
+  <si>
+    <t>9722.1</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>97.2</t>
+  </si>
+  <si>
+    <t>24일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>24일</t>
   </si>
   <si>
     <t>25일</t>
@@ -1128,13 +1140,13 @@
         <v>113</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1142,19 +1154,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1162,19 +1174,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1182,19 +1194,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1202,19 +1214,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1222,19 +1234,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1242,19 +1254,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1262,19 +1274,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-09-01.xlsx
+++ b/past_data/site_8023/2026-09-01.xlsx
@@ -353,10 +353,10 @@
     <t>23일</t>
   </si>
   <si>
-    <t>471.9</t>
-  </si>
-  <si>
-    <t>9722.1</t>
+    <t>472.9</t>
+  </si>
+  <si>
+    <t>9723.1</t>
   </si>
   <si>
     <t>4.7</t>

--- a/past_data/site_8023/2026-09-01.xlsx
+++ b/past_data/site_8023/2026-09-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="129">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>422.7</t>
+    <t>418.2</t>
   </si>
   <si>
     <t>-</t>
@@ -368,10 +368,22 @@
     <t>24일</t>
   </si>
   <si>
+    <t>314.7</t>
+  </si>
+  <si>
+    <t>10037.8</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>100.4</t>
+  </si>
+  <si>
+    <t>25일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>25일</t>
   </si>
   <si>
     <t>26일</t>
@@ -1160,13 +1172,13 @@
         <v>118</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1174,19 +1186,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1194,19 +1206,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1214,19 +1226,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1234,19 +1246,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1254,19 +1266,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1274,19 +1286,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-09-01.xlsx
+++ b/past_data/site_8023/2026-09-01.xlsx
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>418.2</t>
+    <t>418.3</t>
   </si>
   <si>
     <t>-</t>
@@ -368,10 +368,10 @@
     <t>24일</t>
   </si>
   <si>
-    <t>314.7</t>
-  </si>
-  <si>
-    <t>10037.8</t>
+    <t>315.0</t>
+  </si>
+  <si>
+    <t>10038.1</t>
   </si>
   <si>
     <t>3.1</t>

--- a/past_data/site_8023/2026-09-01.xlsx
+++ b/past_data/site_8023/2026-09-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="134">
   <si>
     <t>No.</t>
   </si>
@@ -35,267 +35,270 @@
     <t>평균</t>
   </si>
   <si>
-    <t>418.3</t>
+    <t>406.7</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>80.4</t>
+  </si>
+  <si>
+    <t>0.8</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>206.8</t>
+  </si>
+  <si>
+    <t>287.2</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>2.9</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>534.0</t>
+  </si>
+  <si>
+    <t>821.2</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>8.2</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>553.1</t>
+  </si>
+  <si>
+    <t>1374.3</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>13.7</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
+    <t>523.0</t>
+  </si>
+  <si>
+    <t>1897.3</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>19.0</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
+    <t>495.0</t>
+  </si>
+  <si>
+    <t>2392.3</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>23.9</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
+    <t>565.0</t>
+  </si>
+  <si>
+    <t>2957.3</t>
+  </si>
+  <si>
+    <t>5.7</t>
+  </si>
+  <si>
+    <t>29.6</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
+    <t>544.2</t>
+  </si>
+  <si>
+    <t>3501.5</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
+    <t>35.0</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
+    <t>450.5</t>
+  </si>
+  <si>
+    <t>3952.0</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>39.5</t>
+  </si>
+  <si>
+    <t>10일</t>
+  </si>
+  <si>
+    <t>168.1</t>
+  </si>
+  <si>
+    <t>4120.1</t>
+  </si>
+  <si>
+    <t>1.7</t>
+  </si>
+  <si>
+    <t>41.2</t>
+  </si>
+  <si>
+    <t>11일</t>
+  </si>
+  <si>
+    <t>531.9</t>
+  </si>
+  <si>
+    <t>4652.0</t>
+  </si>
+  <si>
+    <t>46.5</t>
+  </si>
+  <si>
+    <t>12일</t>
+  </si>
+  <si>
+    <t>202.8</t>
+  </si>
+  <si>
+    <t>4854.8</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t>48.5</t>
+  </si>
+  <si>
+    <t>13일</t>
+  </si>
+  <si>
+    <t>181.1</t>
+  </si>
+  <si>
+    <t>5035.9</t>
+  </si>
+  <si>
+    <t>1.8</t>
+  </si>
+  <si>
+    <t>50.4</t>
+  </si>
+  <si>
+    <t>14일</t>
+  </si>
+  <si>
+    <t>343.3</t>
+  </si>
+  <si>
+    <t>5379.2</t>
+  </si>
+  <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>53.8</t>
+  </si>
+  <si>
+    <t>15일</t>
+  </si>
+  <si>
+    <t>502.1</t>
+  </si>
+  <si>
+    <t>5881.3</t>
+  </si>
+  <si>
+    <t>58.8</t>
+  </si>
+  <si>
+    <t>16일</t>
+  </si>
+  <si>
+    <t>557.7</t>
+  </si>
+  <si>
+    <t>6439.0</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>64.4</t>
+  </si>
+  <si>
+    <t>17일</t>
+  </si>
+  <si>
+    <t>381.4</t>
+  </si>
+  <si>
+    <t>6820.4</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>68.2</t>
+  </si>
+  <si>
+    <t>18일</t>
+  </si>
+  <si>
+    <t>424.9</t>
+  </si>
+  <si>
+    <t>7245.3</t>
+  </si>
+  <si>
     <t>4.2</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>80.4</t>
-  </si>
-  <si>
-    <t>0.8</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>206.8</t>
-  </si>
-  <si>
-    <t>287.2</t>
-  </si>
-  <si>
-    <t>2.1</t>
-  </si>
-  <si>
-    <t>2.9</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>534.0</t>
-  </si>
-  <si>
-    <t>821.2</t>
-  </si>
-  <si>
-    <t>5.3</t>
-  </si>
-  <si>
-    <t>8.2</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>553.1</t>
-  </si>
-  <si>
-    <t>1374.3</t>
-  </si>
-  <si>
-    <t>5.5</t>
-  </si>
-  <si>
-    <t>13.7</t>
-  </si>
-  <si>
-    <t>05일</t>
-  </si>
-  <si>
-    <t>523.0</t>
-  </si>
-  <si>
-    <t>1897.3</t>
-  </si>
-  <si>
-    <t>5.2</t>
-  </si>
-  <si>
-    <t>19.0</t>
-  </si>
-  <si>
-    <t>06일</t>
-  </si>
-  <si>
-    <t>495.0</t>
-  </si>
-  <si>
-    <t>2392.3</t>
-  </si>
-  <si>
-    <t>5.0</t>
-  </si>
-  <si>
-    <t>23.9</t>
-  </si>
-  <si>
-    <t>07일</t>
-  </si>
-  <si>
-    <t>565.0</t>
-  </si>
-  <si>
-    <t>2957.3</t>
-  </si>
-  <si>
-    <t>5.7</t>
-  </si>
-  <si>
-    <t>29.6</t>
-  </si>
-  <si>
-    <t>08일</t>
-  </si>
-  <si>
-    <t>544.2</t>
-  </si>
-  <si>
-    <t>3501.5</t>
-  </si>
-  <si>
-    <t>5.4</t>
-  </si>
-  <si>
-    <t>35.0</t>
-  </si>
-  <si>
-    <t>09일</t>
-  </si>
-  <si>
-    <t>450.5</t>
-  </si>
-  <si>
-    <t>3952.0</t>
-  </si>
-  <si>
-    <t>4.5</t>
-  </si>
-  <si>
-    <t>39.5</t>
-  </si>
-  <si>
-    <t>10일</t>
-  </si>
-  <si>
-    <t>168.1</t>
-  </si>
-  <si>
-    <t>4120.1</t>
-  </si>
-  <si>
-    <t>1.7</t>
-  </si>
-  <si>
-    <t>41.2</t>
-  </si>
-  <si>
-    <t>11일</t>
-  </si>
-  <si>
-    <t>531.9</t>
-  </si>
-  <si>
-    <t>4652.0</t>
-  </si>
-  <si>
-    <t>46.5</t>
-  </si>
-  <si>
-    <t>12일</t>
-  </si>
-  <si>
-    <t>202.8</t>
-  </si>
-  <si>
-    <t>4854.8</t>
-  </si>
-  <si>
-    <t>2.0</t>
-  </si>
-  <si>
-    <t>48.5</t>
-  </si>
-  <si>
-    <t>13일</t>
-  </si>
-  <si>
-    <t>181.1</t>
-  </si>
-  <si>
-    <t>5035.9</t>
-  </si>
-  <si>
-    <t>1.8</t>
-  </si>
-  <si>
-    <t>50.4</t>
-  </si>
-  <si>
-    <t>14일</t>
-  </si>
-  <si>
-    <t>343.3</t>
-  </si>
-  <si>
-    <t>5379.2</t>
-  </si>
-  <si>
-    <t>3.4</t>
-  </si>
-  <si>
-    <t>53.8</t>
-  </si>
-  <si>
-    <t>15일</t>
-  </si>
-  <si>
-    <t>502.1</t>
-  </si>
-  <si>
-    <t>5881.3</t>
-  </si>
-  <si>
-    <t>58.8</t>
-  </si>
-  <si>
-    <t>16일</t>
-  </si>
-  <si>
-    <t>557.7</t>
-  </si>
-  <si>
-    <t>6439.0</t>
-  </si>
-  <si>
-    <t>5.6</t>
-  </si>
-  <si>
-    <t>64.4</t>
-  </si>
-  <si>
-    <t>17일</t>
-  </si>
-  <si>
-    <t>381.4</t>
-  </si>
-  <si>
-    <t>6820.4</t>
-  </si>
-  <si>
-    <t>3.8</t>
-  </si>
-  <si>
-    <t>68.2</t>
-  </si>
-  <si>
-    <t>18일</t>
-  </si>
-  <si>
-    <t>424.9</t>
-  </si>
-  <si>
-    <t>7245.3</t>
-  </si>
-  <si>
     <t>72.5</t>
   </si>
   <si>
@@ -383,10 +386,22 @@
     <t>25일</t>
   </si>
   <si>
+    <t>130.5</t>
+  </si>
+  <si>
+    <t>10168.6</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>101.7</t>
+  </si>
+  <si>
+    <t>26일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>26일</t>
   </si>
   <si>
     <t>27일</t>
@@ -1055,10 +1070,10 @@
         <v>93</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>9</v>
+        <v>94</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1066,19 +1081,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1086,19 +1101,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E22" t="s" s="38">
         <v>26</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1106,19 +1121,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E23" t="s" s="33">
         <v>31</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1126,19 +1141,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E24" t="s" s="38">
         <v>36</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1146,19 +1161,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1166,19 +1181,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1186,19 +1201,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1206,19 +1221,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1226,19 +1241,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1246,19 +1261,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1266,19 +1281,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1286,19 +1301,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-09-01.xlsx
+++ b/past_data/site_8023/2026-09-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="138">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>406.7</t>
+    <t>406.3</t>
   </si>
   <si>
     <t>-</t>
@@ -401,10 +401,22 @@
     <t>26일</t>
   </si>
   <si>
+    <t>394.4</t>
+  </si>
+  <si>
+    <t>10563.0</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>105.6</t>
+  </si>
+  <si>
+    <t>27일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>27일</t>
   </si>
   <si>
     <t>28일</t>
@@ -1227,13 +1239,13 @@
         <v>129</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1241,19 +1253,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1261,19 +1273,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1281,19 +1293,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1301,19 +1313,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-09-01.xlsx
+++ b/past_data/site_8023/2026-09-01.xlsx
@@ -401,10 +401,10 @@
     <t>26일</t>
   </si>
   <si>
-    <t>394.4</t>
-  </si>
-  <si>
-    <t>10563.0</t>
+    <t>394.8</t>
+  </si>
+  <si>
+    <t>10563.4</t>
   </si>
   <si>
     <t>3.9</t>

--- a/past_data/site_8023/2026-09-01.xlsx
+++ b/past_data/site_8023/2026-09-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="142">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>406.3</t>
+    <t>409.5</t>
   </si>
   <si>
     <t>-</t>
@@ -416,10 +416,22 @@
     <t>27일</t>
   </si>
   <si>
+    <t>492.8</t>
+  </si>
+  <si>
+    <t>11056.2</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>110.6</t>
+  </si>
+  <si>
+    <t>28일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>28일</t>
   </si>
   <si>
     <t>29일</t>
@@ -1259,13 +1271,13 @@
         <v>134</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1273,19 +1285,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1293,19 +1305,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1313,19 +1325,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-09-01.xlsx
+++ b/past_data/site_8023/2026-09-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="145">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>409.5</t>
+    <t>409.3</t>
   </si>
   <si>
     <t>-</t>
@@ -431,10 +431,19 @@
     <t>28일</t>
   </si>
   <si>
+    <t>405.2</t>
+  </si>
+  <si>
+    <t>11461.4</t>
+  </si>
+  <si>
+    <t>114.6</t>
+  </si>
+  <si>
+    <t>29일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>29일</t>
   </si>
   <si>
     <t>30일</t>
@@ -1291,13 +1300,13 @@
         <v>139</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>139</v>
+        <v>9</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1305,19 +1314,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1325,19 +1334,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-09-01.xlsx
+++ b/past_data/site_8023/2026-09-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="149">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>409.3</t>
+    <t>411.8</t>
   </si>
   <si>
     <t>-</t>
@@ -443,10 +443,22 @@
     <t>29일</t>
   </si>
   <si>
+    <t>480.5</t>
+  </si>
+  <si>
+    <t>11941.9</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>119.4</t>
+  </si>
+  <si>
+    <t>30일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>30일</t>
   </si>
 </sst>
 </file>
@@ -1320,13 +1332,13 @@
         <v>143</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1334,19 +1346,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-09-01.xlsx
+++ b/past_data/site_8023/2026-09-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="152">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>411.8</t>
+    <t>413.3</t>
   </si>
   <si>
     <t>-</t>
@@ -458,7 +458,16 @@
     <t>30일</t>
   </si>
   <si>
-    <t>0.0</t>
+    <t>457.8</t>
+  </si>
+  <si>
+    <t>12399.7</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>124.0</t>
   </si>
 </sst>
 </file>
@@ -1352,13 +1361,13 @@
         <v>148</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
